--- a/daily_matches/job_matches_2026-07-29.xlsx
+++ b/daily_matches/job_matches_2026-07-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Artificial Analysis</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>24.4</v>
+        <v>12.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Gemini, Pinecone, TensorFlow, PyTorch, MLflow, FastAPI</t>
+          <t>RAG, Hugging Face, PyTorch, CI/CD, Git, PostgreSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,137 +496,137 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a4a763e4890e197</t>
+          <t>https://www.indeed.com/viewjob?jk=7fd8314fe44c7467</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Senior Automation Tester</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>24.4</v>
+        <v>10</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Gemini, Pinecone, TensorFlow, PyTorch, MLflow, FastAPI</t>
+          <t>RAG, Kubernetes, AKS, CI/CD, Git, SQL, R, Java, Optimization</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b63d700b95b8e4e4</t>
+          <t>https://www.indeed.com/viewjob?jk=9745b7b89c5ec283</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Gen AI Sr. Engineer</t>
+          <t>Data Analytics and Research Analyst</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>Serco</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.8</v>
+        <v>10</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Gemini, Prompt Engineering, BigQuery, Docker, Kubernetes, CI/CD, Terraform</t>
+          <t>RAG, Redshift, Databricks, Redshift, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b0e218931bd7dc3</t>
+          <t>https://www.indeed.com/viewjob?jk=632275ea7bb2d520</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Azure DevOps Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ImagineX Consulting</t>
+          <t>Not A Customers Hiring Org</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>10</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, SQL</t>
+          <t>Data Scientist, TensorFlow, PyTorch, XGBoost, Databricks, Python, SQL, R, Hypothesis Testing</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9cba82380663ee6</t>
+          <t>https://www.indeed.com/viewjob?jk=b692a42ba1dbdbfc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Scientist II</t>
+          <t>Software Engineer – AI Evaluation &amp; Automation</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Republic Services</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>10</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Copilot, Prompt Engineering, Git, Snowflake, Python, SQL, R</t>
+          <t>Generative AI, RAG, Docker, CI/CD, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,252 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d653723daaba2e1</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Gemini, Docker, Kubernetes, CI/CD, Git, NoSQL, SQL, R</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2c14c97c69cc0bb1</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Process Automation Engineer</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Stored Energy Systems</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Longmont, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Copilot, Git, Power BI, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5048cfb1b56df0af</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>AI Full Stack Engineer (Prime Brokerage Technology)</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Morgan Stanley</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>LangChain, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4120fbc61ab47243</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Optum</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Raleigh, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Copilot, Data Lake, Git, Databricks, Kafka, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=833d80634f5fd65f</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Senior Platform Engineer (Job ID 3021452)</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>ADT</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Irving, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>10</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Copilot, Docker, Kubernetes, CI/CD, Git, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=884edaf005df48f0</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Data Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Broccoli AI</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>10</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>RAG, Redshift, BigQuery, Snowflake, BigQuery, Redshift, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a51b920579cc4760</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Senior Data Analytics and Research Analyst</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Serco</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Herndon, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>10</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>RAG, Redshift, Databricks, Redshift, Tableau, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cb127f44de68712e</t>
+          <t>https://www.indeed.com/viewjob?jk=a6e99c877c17c9a2</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-29.xlsx
+++ b/daily_matches/job_matches_2026-07-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>AWS ETL Data Engineer - HYBRID</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Artificial Analysis</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>12.2</v>
+        <v>17.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Hugging Face, PyTorch, CI/CD, Git, PostgreSQL, Python, SQL, R, Java</t>
+          <t>RAG, S3, EC2, Glue, Redshift, Git, Redshift, PySpark, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fd8314fe44c7467</t>
+          <t>https://www.indeed.com/viewjob?jk=0f3b0a20014410c8</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Automation Tester</t>
+          <t>Software Developer / Senior Software Developer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>Kinsale Management Inc</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, AKS, CI/CD, Git, SQL, R, Java, Optimization</t>
+          <t>Generative AI, RAG, Copilot, Docker, CI/CD, Git, Kafka, Python, SQL, R</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9745b7b89c5ec283</t>
+          <t>https://www.indeed.com/viewjob?jk=90cafd9581b6764f</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Analytics and Research Analyst</t>
+          <t>Senior Data Engineer, Finance</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Serco</t>
+          <t>Genesys</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Redshift, Databricks, Redshift, Tableau, Power BI, Python, SQL, R</t>
+          <t>RAG, S3, Glue, CI/CD, Git, Snowflake, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,77 +566,182 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=632275ea7bb2d520</t>
+          <t>https://www.indeed.com/viewjob?jk=15db7e3fdebd8bb4</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Sr Applied Data Scientist - RecSys (applied ML, PyTorch, ML Ops)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Not A Customers Hiring Org</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, TensorFlow, PyTorch, XGBoost, Databricks, Python, SQL, R, Hypothesis Testing</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, PyTorch, Git, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b692a42ba1dbdbfc</t>
+          <t>https://www.indeed.com/viewjob?jk=b612865a8f3df300</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer – AI Evaluation &amp; Automation</t>
+          <t>Backend &amp; AI/ML Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, Docker, Kubernetes, CI/CD, Git, Databricks, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5aa53d8625c26d40</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>DevOps &amp; Data Engineer - GCP (Google Cloud Platform)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Alpharetta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, CI/CD, Terraform, Git, Databricks, BigQuery, Kafka, R, Scala</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2620c8155640eadb</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>DONNELLEY FINANCIAL SOLUTIONS</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
         <v>10</v>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Docker, CI/CD, Git, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Copilot, CI/CD, Git, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a6b9605cbed0db34</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Sr. Engineer - Data Center Automation (Frontend)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Brooklyn Park, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>10</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>RAG, AKS, CI/CD, PostgreSQL, MongoDB, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a6e99c877c17c9a2</t>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d481ecc34e1f75ae</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-29.xlsx
+++ b/daily_matches/job_matches_2026-07-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AWS ETL Data Engineer - HYBRID</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>ZS Associates</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.8</v>
+        <v>26.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Glue, Redshift, Git, Redshift, PySpark, Kafka, MySQL</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Pinecone, Prompt Engineering, TensorFlow, PyTorch, Keras</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,67 +496,67 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f3b0a20014410c8</t>
+          <t>https://www.indeed.com/viewjob?jk=23b0d8efe2a85a6a</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Developer / Senior Software Developer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kinsale Management Inc</t>
+          <t>ZS Associates</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.3</v>
+        <v>26.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Docker, CI/CD, Git, Kafka, Python, SQL, R</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Pinecone, Prompt Engineering, TensorFlow, PyTorch, Keras</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90cafd9581b6764f</t>
+          <t>https://www.indeed.com/viewjob?jk=e9bb6b2adb25c47c</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Finance</t>
+          <t>Azure Data Engineer with Elasticsearch Experience</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Genesys</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12.2</v>
+        <v>20</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, CI/CD, Git, Snowflake, Python, SQL, R, Scala</t>
+          <t>Data Scientist, RAG, Copilot, FastAPI, Docker, AKS, CI/CD, Terraform, Git, Databricks</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,137 +566,137 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15db7e3fdebd8bb4</t>
+          <t>https://www.indeed.com/viewjob?jk=e7528008cee1ab91</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr Applied Data Scientist - RecSys (applied ML, PyTorch, ML Ops)</t>
+          <t>Gen AI Tech Consultant Bloomfield CT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>IPolarity LLC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.2</v>
+        <v>20</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, PyTorch, Git, Python, SQL, R, Scala</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Pinecone, Prompt Engineering, S3, EC2, Glue, FastAPI</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b612865a8f3df300</t>
+          <t>https://www.indeed.com/viewjob?jk=504858d7129323d8</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Backend &amp; AI/ML Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.1</v>
+        <v>18.9</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Docker, Kubernetes, CI/CD, Git, Databricks, Python, R, Scala</t>
+          <t>LangChain, RAG, Copilot, FastAPI, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5aa53d8625c26d40</t>
+          <t>https://www.indeed.com/viewjob?jk=315bf48175d7a712</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DevOps &amp; Data Engineer - GCP (Google Cloud Platform)</t>
+          <t>GenAI Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.1</v>
+        <v>18.9</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, CI/CD, Terraform, Git, Databricks, BigQuery, Kafka, R, Scala</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Gemini, Prompt Engineering, BigQuery, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2620c8155640eadb</t>
+          <t>https://www.indeed.com/viewjob?jk=d7ff6073572b730f</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI Platform Architect, Strategy and Enablement</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DONNELLEY FINANCIAL SOLUTIONS</t>
+          <t>EisnerAmper</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, CI/CD, Git, SQL, R, Java, Scala</t>
+          <t>AI Engineer, RAG, Synapse, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Databricks</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,42 +706,637 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6b9605cbed0db34</t>
+          <t>https://www.indeed.com/viewjob?jk=e316e9f322e85e11</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr. Engineer - Data Center Automation (Frontend)</t>
+          <t>Senior Machine Learning Ops Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>National Debt Relief</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Generative AI, BigQuery, MLflow, FastAPI, Docker, Kubernetes, CI/CD, Terraform, Snowflake, Databricks</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7a56ad8bd3fa9afc</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Sr. Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Addepar</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e565e5bf02069402</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Senior GCP CloudOps Engineer</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Cotiviti</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, Docker, Kubernetes, CI/CD, Terraform, Git, BigQuery, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=78a58a30f511c5e2</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Agentic AI Developer IV</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>RealPage Inc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Richardson, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2aa74782c6547bac</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Software Engineer - Java / SQL / AI Dev</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Cotiviti</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, S3, EC2, Git, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=42f1ac19c69767df</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Research Triangle Park, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, CI/CD, GitHub Actions, Git, Dask, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e7af0ff1bd166b09</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CA, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>AI Engineer, Glue, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=626b97d1a80296b3</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Data Scientist - Applied AI/ML Senior Associate</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, Kubernetes, CI/CD, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c547acb20784d91e</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Senior Generative AI Scientist I</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Cotiviti</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Mistral, TensorFlow, PyTorch, Keras, NLTK</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b2ce6e6d028514b2</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Senior AI Application Engineer</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Alchemy</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3ad5c12b0e95091e</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>TELI.AI</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Southfield, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Git, PostgreSQL, MySQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d9c05124b8dec3eb</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Software Developer/Engineer (Mid Level experience)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Tech Army</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, Mistral, Hugging Face, Prompt Engineering, Docker, Kubernetes, Python, R</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a6f18d29ec176094</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>SysLogic, Inc.</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Brookfield, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
         <v>10</v>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>RAG, AKS, CI/CD, PostgreSQL, MongoDB, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d481ecc34e1f75ae</t>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RAG, Synapse, Data Lake, CI/CD, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4dd438012cba0523</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Minnetonka, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>10</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, CI/CD, MongoDB, NoSQL, Power BI, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e3aa33c81bfc5b10</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Python Software Engineer (Jr–Mid Level)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Stellar Solutions</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Fremont, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>10</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Generative AI, TensorFlow, PyTorch, MySQL, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=091d68ed798a144d</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>THEMESOFT</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Chandler, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, BigQuery, Data Lake, BigQuery, PySpark, Kafka, Python, R</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b70fa6f0b43880b3</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Forward Deployed Engineer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Robots &amp; Pencils</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>10</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Docker, Kubernetes, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c48206884f609a7d</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Cornell University</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ithaca, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>10</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=494cd6c14442cd57</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-29.xlsx
+++ b/daily_matches/job_matches_2026-07-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,95 +468,95 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Solutions Engineer - East Coast</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ZS Associates</t>
+          <t>Cloudera</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>26.7</v>
+        <v>16.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Pinecone, Prompt Engineering, TensorFlow, PyTorch, Keras</t>
+          <t>RAG, Data Lake, Kubernetes, Git, Kafka, Hadoop, MongoDB, Cassandra, NoSQL, Tableau</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23b0d8efe2a85a6a</t>
+          <t>https://www.indeed.com/viewjob?jk=c3467fd4232b4427</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ZS Associates</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>26.7</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Pinecone, Prompt Engineering, TensorFlow, PyTorch, Keras</t>
+          <t>Copilot, Redshift, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Redshift, Kafka</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9bb6b2adb25c47c</t>
+          <t>https://www.indeed.com/viewjob?jk=355105231092b986</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Azure Data Engineer with Elasticsearch Experience</t>
+          <t>AI Solutions Architect</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Confiz</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Copilot, FastAPI, Docker, AKS, CI/CD, Terraform, Git, Databricks</t>
+          <t>RAG, Pinecone, Prompt Engineering, Cortex, MLflow, Docker, Kubernetes, Terraform, Snowflake, Databricks</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7528008cee1ab91</t>
+          <t>https://www.indeed.com/viewjob?jk=0691b5cf974ba456</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Gen AI Tech Consultant Bloomfield CT</t>
+          <t>Software Engineer II - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>IPolarity LLC</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>20</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Pinecone, Prompt Engineering, S3, EC2, Glue, FastAPI</t>
+          <t>Generative AI, RAG, BigQuery, Apache Airflow, CI/CD, Git, BigQuery, PySpark, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=504858d7129323d8</t>
+          <t>https://www.indeed.com/viewjob?jk=a4e43dcb8c0d20cc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Epsilon</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Wakefield, MA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.9</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Copilot, FastAPI, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform</t>
+          <t>LangChain, RAG, Copilot, Pinecone, Prompt Engineering, Docker, Kubernetes, Jenkins, Terraform, Git</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=315bf48175d7a712</t>
+          <t>https://www.indeed.com/viewjob?jk=e267c7780d11420c</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GenAI Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>DASi LLC</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Doral, FL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.9</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, Gemini, Prompt Engineering, BigQuery, Docker, Kubernetes, CI/CD</t>
+          <t>AI Engineer, Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Terraform, Git, SQL, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7ff6073572b730f</t>
+          <t>https://www.indeed.com/viewjob?jk=1a9b9bac4a9c92e3</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AI Platform Architect, Strategy and Enablement</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>EisnerAmper</t>
+          <t>NinjaOne</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Synapse, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Databricks</t>
+          <t>Data Scientist, Generative AI, RAG, Kinesis, Databricks, Kafka, Tableau, Python, SQL, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,54 +706,54 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e316e9f322e85e11</t>
+          <t>https://www.indeed.com/viewjob?jk=5135e6c341a3ad15</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Ops Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>National Debt Relief</t>
+          <t>NinjaOne</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Generative AI, BigQuery, MLflow, FastAPI, Docker, Kubernetes, CI/CD, Terraform, Snowflake, Databricks</t>
+          <t>Data Scientist, Generative AI, RAG, Kinesis, Databricks, Kafka, Tableau, Python, SQL, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a56ad8bd3fa9afc</t>
+          <t>https://www.indeed.com/viewjob?jk=da990d9cbb7af601</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr. Automation Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Addepar</t>
+          <t>NinjaOne</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>Data Scientist, Generative AI, RAG, Kinesis, Databricks, Kafka, Tableau, Python, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,19 +776,19 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e565e5bf02069402</t>
+          <t>https://www.indeed.com/viewjob?jk=e2340325e41c8560</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior GCP CloudOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>NinjaOne</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -801,64 +801,64 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Docker, Kubernetes, CI/CD, Terraform, Git, BigQuery, Python, SQL</t>
+          <t>Data Scientist, Generative AI, RAG, Kinesis, Databricks, Kafka, Tableau, Python, SQL, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78a58a30f511c5e2</t>
+          <t>https://www.indeed.com/viewjob?jk=37729657de7d9789</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Agentic AI Developer IV</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>RealPage Inc</t>
+          <t>NinjaOne</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Git, Python, R, Java</t>
+          <t>Data Scientist, Generative AI, RAG, Kinesis, Databricks, Kafka, Tableau, Python, SQL, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2aa74782c6547bac</t>
+          <t>https://www.indeed.com/viewjob?jk=8181bc68066c8b55</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineer - Java / SQL / AI Dev</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>NinjaOne</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -867,46 +867,46 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, S3, EC2, Git, Python, SQL</t>
+          <t>Data Scientist, Generative AI, RAG, Kinesis, Databricks, Kafka, Tableau, Python, SQL, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42f1ac19c69767df</t>
+          <t>https://www.indeed.com/viewjob?jk=48b451377b7721ec</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NinjaOne</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, CI/CD, GitHub Actions, Git, Dask, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, RAG, Kinesis, Databricks, Kafka, Tableau, Python, SQL, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7af0ff1bd166b09</t>
+          <t>https://www.indeed.com/viewjob?jk=fef2706cf7bdf47b</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NinjaOne</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AI Engineer, Glue, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, RAG, Kinesis, Databricks, Kafka, Tableau, Python, SQL, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=626b97d1a80296b3</t>
+          <t>https://www.indeed.com/viewjob?jk=29a938574a04d8af</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Scientist - Applied AI/ML Senior Associate</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>NinjaOne</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, Kubernetes, CI/CD, Git, Python, R</t>
+          <t>Data Scientist, Generative AI, RAG, Kinesis, Databricks, Kafka, Tableau, Python, SQL, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,19 +986,19 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c547acb20784d91e</t>
+          <t>https://www.indeed.com/viewjob?jk=9b6904bf6d9729d3</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Generative AI Scientist I</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>NinjaOne</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1007,46 +1007,46 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Mistral, TensorFlow, PyTorch, Keras, NLTK</t>
+          <t>Data Scientist, Generative AI, RAG, Kinesis, Databricks, Kafka, Tableau, Python, SQL, R</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2ce6e6d028514b2</t>
+          <t>https://www.indeed.com/viewjob?jk=c6c49f8e442d9741</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior AI Application Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Alchemy</t>
+          <t>NinjaOne</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, Python, R, Scala, Optimization</t>
+          <t>Data Scientist, Generative AI, RAG, Kinesis, Databricks, Kafka, Tableau, Python, SQL, R</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ad5c12b0e95091e</t>
+          <t>https://www.indeed.com/viewjob?jk=5dd948a47e1b583a</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>TELI.AI</t>
+          <t>NinjaOne</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Southfield, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Git, PostgreSQL, MySQL, Python, SQL, R, Java, Scala</t>
+          <t>Data Scientist, Generative AI, RAG, Kinesis, Databricks, Kafka, Tableau, Python, SQL, R</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9c05124b8dec3eb</t>
+          <t>https://www.indeed.com/viewjob?jk=6ce2b7cd2b44134b</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Developer/Engineer (Mid Level experience)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Tech Army</t>
+          <t>NinjaOne</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Mistral, Hugging Face, Prompt Engineering, Docker, Kubernetes, Python, R</t>
+          <t>Data Scientist, Generative AI, RAG, Kinesis, Databricks, Kafka, Tableau, Python, SQL, R</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6f18d29ec176094</t>
+          <t>https://www.indeed.com/viewjob?jk=2e5a8f41ef5eb310</t>
         </is>
       </c>
     </row>
@@ -1138,20 +1138,20 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SysLogic, Inc.</t>
+          <t>NinjaOne</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brookfield, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Data Lake, CI/CD, Power BI, Python, SQL, R, Scala</t>
+          <t>Data Scientist, Generative AI, RAG, Kinesis, Databricks, Kafka, Tableau, Python, SQL, R</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4dd438012cba0523</t>
+          <t>https://www.indeed.com/viewjob?jk=93518b57b5322a19</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>NinjaOne</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, CI/CD, MongoDB, NoSQL, Power BI, SQL, R, Optimization</t>
+          <t>Data Scientist, Generative AI, RAG, Kinesis, Databricks, Kafka, Tableau, Python, SQL, R</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3aa33c81bfc5b10</t>
+          <t>https://www.indeed.com/viewjob?jk=308e79781d5fdd4d</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Python Software Engineer (Jr–Mid Level)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Stellar Solutions</t>
+          <t>NinjaOne</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Generative AI, TensorFlow, PyTorch, MySQL, Python, SQL, R, Scala, Optimization</t>
+          <t>Data Scientist, Generative AI, RAG, Kinesis, Databricks, Kafka, Tableau, Python, SQL, R</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=091d68ed798a144d</t>
+          <t>https://www.indeed.com/viewjob?jk=7b7aa55995bbc05a</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>THEMESOFT</t>
+          <t>NinjaOne</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Chandler, IN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>LangChain, RAG, BigQuery, Data Lake, BigQuery, PySpark, Kafka, Python, R</t>
+          <t>Data Scientist, Generative AI, RAG, Kinesis, Databricks, Kafka, Tableau, Python, SQL, R</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,19 +1266,19 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b70fa6f0b43880b3</t>
+          <t>https://www.indeed.com/viewjob?jk=15ece6abd61c2f49</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Robots &amp; Pencils</t>
+          <t>NinjaOne</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1287,11 +1287,11 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Docker, Kubernetes, Python, R, Scala, Optimization</t>
+          <t>Data Scientist, Generative AI, RAG, Kinesis, Databricks, Kafka, Tableau, Python, SQL, R</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,42 +1301,497 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c48206884f609a7d</t>
+          <t>https://www.indeed.com/viewjob?jk=42b0162216071e81</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Data Engineer (ETL Developer) US CITIZENS ONLY</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Cornell University</t>
+          <t>redan</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Ithaca, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RAG, S3, Glue, Redshift, CI/CD, Terraform, Redshift, PySpark, PostgreSQL, Python</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b7e83b43e3fd593d</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer - Agentic Systems &amp; Data Pipelines</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Collaboration.Ai</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, S3, Kinesis, FastAPI, Docker, Kubernetes, Kafka, PostgreSQL, Python</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=94a3010a0172bde1</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Software Engineer L3</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Twilio</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>IN, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Kubernetes, CI/CD, Terraform, Git, Kafka, NoSQL, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=42841dc64210d93f</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>DevOPS Engineer - Irving, TX (ONSITE)</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Kore.ai</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Generative AI, Kubernetes, AKS, CI/CD, Jenkins, PostgreSQL, MySQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=27639b7b075aa034</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>LLaMA, Gemini, Copilot, Prompt Engineering, Git, MySQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=494fe8e48cd6d62b</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Data Engineer I - Global Servicing Technology</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>American Express</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, CI/CD, Jenkins, Git, BigQuery, NoSQL, Power BI, SQL, R</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=18d4e19e765bcde9</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Senior Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>accrete</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=504028cfd0bf3313</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>M365 Copilot Software Engineer</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Genpact</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Copilot, CI/CD, GitHub Actions, Git, SQL, R</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fdd59cdf3c026fb0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>The Washington Post</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, S3, Git, PostgreSQL, MongoDB, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3f9aec2a1b87419d</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Data Scientist 35511</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Juncos, PR, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Data Lake, Git, Tableau, Power BI, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=61649d2a73b25b98</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Guardian Life</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Bethlehem, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
         <v>10</v>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=494cd6c14442cd57</t>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Git, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2bc8e71462d55a4e</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>AI/ML Engineer &amp; Data Management Specialist</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Sabre Systems</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Naval Air Station Patuxent River, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>10</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, S3, Git, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=586c6efb0afc6398</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Full Stack Software Engineer, Data (Starlink)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>SpaceX</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Redmond, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>10</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, Kafka, PostgreSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8cac76c6b23f2063</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Analyst, Applied AI Solutions</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>10</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, Copilot, Git, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1f9dd8c06623b61b</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-29.xlsx
+++ b/daily_matches/job_matches_2026-07-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Solutions Engineer - East Coast</t>
+          <t>AI Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Cloudera</t>
+          <t>University of Texas at Austin</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,7 +486,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Kubernetes, Git, Kafka, Hadoop, MongoDB, Cassandra, NoSQL, Tableau</t>
+          <t>AI Engineer, Generative AI, Gemini, Copilot, Pinecone, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3467fd4232b4427</t>
+          <t>https://www.indeed.com/viewjob?jk=8523f45b800a98d2</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Junior AI Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Trellance</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Copilot, Redshift, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Redshift, Kafka</t>
+          <t>AI Engineer, Generative AI, RAG, Pinecone, Cortex, CI/CD, Snowflake, Databricks, Tableau, Power BI</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=355105231092b986</t>
+          <t>https://www.indeed.com/viewjob?jk=6cfec0ee79a36d0b</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI Solutions Architect</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Confiz</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Pinecone, Prompt Engineering, Cortex, MLflow, Docker, Kubernetes, Terraform, Snowflake, Databricks</t>
+          <t>RAG, S3, Redshift, Docker, Kubernetes, Terraform, Redshift, PostgreSQL, MongoDB, Python</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0691b5cf974ba456</t>
+          <t>https://www.indeed.com/viewjob?jk=2b734deb5b5c4fd4</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer II - Global Servicing Technology</t>
+          <t>Senior Software Engineer, Global Banking &amp; Markets, AI/ML Technology</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, BigQuery, Apache Airflow, CI/CD, Git, BigQuery, PySpark, Kafka, NoSQL</t>
+          <t>RAG, Gemini, Copilot, Docker, Kubernetes, CI/CD, Git, Kafka, NoSQL, SQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4e43dcb8c0d20cc</t>
+          <t>https://www.indeed.com/viewjob?jk=1483d6cac3aa3128</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Engineering-L2-Dallas-Analyst-Software Engineering</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Epsilon</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Wakefield, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Copilot, Pinecone, Prompt Engineering, Docker, Kubernetes, Jenkins, Terraform, Git</t>
+          <t>RAG, Kubernetes, AKS, CI/CD, Snowflake, Databricks, Kafka, Hadoop, Python, SQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e267c7780d11420c</t>
+          <t>https://www.indeed.com/viewjob?jk=334f6eafa2204917</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI/ML Engineer (Senior Associate) - Remote</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DASi LLC</t>
+          <t>Huron Consulting Group</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Doral, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Terraform, Git, SQL, R</t>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, AWS SageMaker, FastAPI, Docker, CI/CD</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a9b9bac4a9c92e3</t>
+          <t>https://www.indeed.com/viewjob?jk=1bb67d4138266183</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NinjaOne</t>
+          <t>The Weather Company</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Andover, MA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Kinesis, Databricks, Kafka, Tableau, Python, SQL, R</t>
+          <t>RAG, Copilot, S3, EC2, Docker, Kubernetes, CI/CD, Git, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5135e6c341a3ad15</t>
+          <t>https://www.indeed.com/viewjob?jk=34cf04c12e423597</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NinjaOne</t>
+          <t>Ascendion</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Redmond, WA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Kinesis, Databricks, Kafka, Tableau, Python, SQL, R</t>
+          <t>RAG, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, MongoDB, SQL, R, Java</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da990d9cbb7af601</t>
+          <t>https://www.indeed.com/viewjob?jk=0a8fea0d6fbd1cf6</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NinjaOne</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Kinesis, Databricks, Kafka, Tableau, Python, SQL, R</t>
+          <t>FastAPI, Docker, Kubernetes, GitHub Actions, Git, Kafka, PostgreSQL, MongoDB, Python, SQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2340325e41c8560</t>
+          <t>https://www.indeed.com/viewjob?jk=0e5d9c9078da0cac</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NinjaOne</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Kinesis, Databricks, Kafka, Tableau, Python, SQL, R</t>
+          <t>LLaMA, Gemini, Copilot, Prompt Engineering, Git, MySQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37729657de7d9789</t>
+          <t>https://www.indeed.com/viewjob?jk=caf82fff4ed5ef31</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NinjaOne</t>
+          <t>True Classic</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Calabasas, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Kinesis, Databricks, Kafka, Tableau, Python, SQL, R</t>
+          <t>AI Engineer, RAG, Prompt Engineering, CI/CD, Git, PostgreSQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8181bc68066c8b55</t>
+          <t>https://www.indeed.com/viewjob?jk=3fc9c743e0a349ef</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NinjaOne</t>
+          <t>Leidos</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Kinesis, Databricks, Kafka, Tableau, Python, SQL, R</t>
+          <t>Data Scientist, RAG, Apache Airflow, CI/CD, Git, Databricks, PySpark, Python, SQL, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48b451377b7721ec</t>
+          <t>https://www.indeed.com/viewjob?jk=002cb1d712286720</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Scientist ll - Digital Intelligence</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>NinjaOne</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Kinesis, Databricks, Kafka, Tableau, Python, SQL, R</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, XGBoost, Git, Databricks, PySpark, Python, SQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fef2706cf7bdf47b</t>
+          <t>https://www.indeed.com/viewjob?jk=5ba5b1d946790692</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AI Engineer, Conversational AI &amp; Agentic Systems - Voice Required</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>NinjaOne</t>
+          <t>Blooming Health</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Kinesis, Databricks, Kafka, Tableau, Python, SQL, R</t>
+          <t>AI Engineer, RAG, Prompt Engineering, Docker, Kubernetes, Kafka, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29a938574a04d8af</t>
+          <t>https://www.indeed.com/viewjob?jk=5e7979301289c696</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>NinjaOne</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Kinesis, Databricks, Kafka, Tableau, Python, SQL, R</t>
+          <t>RAG, S3, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b6904bf6d9729d3</t>
+          <t>https://www.indeed.com/viewjob?jk=262c117f16e0e490</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>NinjaOne</t>
+          <t>Delinea</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Kinesis, Databricks, Kafka, Tableau, Python, SQL, R</t>
+          <t>RAG, Kubernetes, CI/CD, Terraform, Kafka, NoSQL, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6c49f8e442d9741</t>
+          <t>https://www.indeed.com/viewjob?jk=749e23d0b9c802de</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack AI Software Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>NinjaOne</t>
+          <t>Freedom Mortgage</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Marlton, NJ, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Kinesis, Databricks, Kafka, Tableau, Python, SQL, R</t>
+          <t>AI Engineer, RAG, Copilot, Kubernetes, Git, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5dd948a47e1b583a</t>
+          <t>https://www.indeed.com/viewjob?jk=9bf2e8dc44b5e2c3</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer, Big Data and Cloud</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>NinjaOne</t>
+          <t>Vistar Media</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Kinesis, Databricks, Kafka, Tableau, Python, SQL, R</t>
+          <t>Data Scientist, RAG, BigQuery, Git, BigQuery, Kafka, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ce2b7cd2b44134b</t>
+          <t>https://www.indeed.com/viewjob?jk=488613eddf36a539</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>NinjaOne</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.4</v>
+        <v>10</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Kinesis, Databricks, Kafka, Tableau, Python, SQL, R</t>
+          <t>RAG, FastAPI, Docker, CI/CD, Git, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e5a8f41ef5eb310</t>
+          <t>https://www.indeed.com/viewjob?jk=d51bf7d637343fc1</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NinjaOne</t>
+          <t>Peterson Caterpillar</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Leandro, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.4</v>
+        <v>10</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Kinesis, Databricks, Kafka, Tableau, Python, SQL, R</t>
+          <t>RAG, Snowflake, PySpark, Power BI, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93518b57b5322a19</t>
+          <t>https://www.indeed.com/viewjob?jk=c6d496ec22a09d07</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Reliability Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>NinjaOne</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.4</v>
+        <v>10</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Kinesis, Databricks, Kafka, Tableau, Python, SQL, R</t>
+          <t>RAG, Copilot, Kubernetes, CI/CD, Terraform, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=308e79781d5fdd4d</t>
+          <t>https://www.indeed.com/viewjob?jk=eed01edaf71cb8e2</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Reliability Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>NinjaOne</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.4</v>
+        <v>10</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Kinesis, Databricks, Kafka, Tableau, Python, SQL, R</t>
+          <t>RAG, Copilot, Kubernetes, CI/CD, Terraform, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b7aa55995bbc05a</t>
+          <t>https://www.indeed.com/viewjob?jk=894e91b00b84ec52</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Reliability Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>NinjaOne</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.4</v>
+        <v>10</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Kinesis, Databricks, Kafka, Tableau, Python, SQL, R</t>
+          <t>RAG, Copilot, Kubernetes, CI/CD, Terraform, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15ece6abd61c2f49</t>
+          <t>https://www.indeed.com/viewjob?jk=015ed88153be94e8</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Reliability Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>NinjaOne</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.4</v>
+        <v>10</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Kinesis, Databricks, Kafka, Tableau, Python, SQL, R</t>
+          <t>RAG, Copilot, Kubernetes, CI/CD, Terraform, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42b0162216071e81</t>
+          <t>https://www.indeed.com/viewjob?jk=9330891927556077</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer (ETL Developer) US CITIZENS ONLY</t>
+          <t>Sr Data Analyst</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>redan</t>
+          <t>Guild Mortgage Company LLC</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.4</v>
+        <v>10</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Redshift, CI/CD, Terraform, Redshift, PySpark, PostgreSQL, Python</t>
+          <t>RAG, Snowflake, MySQL, MongoDB, Cassandra, NoSQL, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,462 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7e83b43e3fd593d</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Senior AI Engineer - Agentic Systems &amp; Data Pipelines</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Collaboration.Ai</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, S3, Kinesis, FastAPI, Docker, Kubernetes, Kafka, PostgreSQL, Python</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=94a3010a0172bde1</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Software Engineer L3</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Twilio</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>IN, US USA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Kubernetes, CI/CD, Terraform, Git, Kafka, NoSQL, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=42841dc64210d93f</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>DevOPS Engineer - Irving, TX (ONSITE)</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Kore.ai</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Irving, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Generative AI, Kubernetes, AKS, CI/CD, Jenkins, PostgreSQL, MySQL, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=27639b7b075aa034</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Visa</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>LLaMA, Gemini, Copilot, Prompt Engineering, Git, MySQL, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=494fe8e48cd6d62b</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Data Engineer I - Global Servicing Technology</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>American Express</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>RAG, BigQuery, CI/CD, Jenkins, Git, BigQuery, NoSQL, Power BI, SQL, R</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=18d4e19e765bcde9</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Senior Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>accrete</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=504028cfd0bf3313</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>M365 Copilot Software Engineer</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Genpact</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Copilot, CI/CD, GitHub Actions, Git, SQL, R</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fdd59cdf3c026fb0</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>The Washington Post</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, S3, Git, PostgreSQL, MongoDB, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3f9aec2a1b87419d</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Data Scientist 35511</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Juncos, PR, US USA</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Data Lake, Git, Tableau, Power BI, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=61649d2a73b25b98</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Guardian Life</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Bethlehem, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>10</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>RAG, Docker, CI/CD, Git, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2bc8e71462d55a4e</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>AI/ML Engineer &amp; Data Management Specialist</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Sabre Systems</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Naval Air Station Patuxent River, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>10</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>RAG, Prompt Engineering, S3, Git, Tableau, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=586c6efb0afc6398</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Full Stack Software Engineer, Data (Starlink)</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>SpaceX</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Redmond, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>10</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>RAG, Data Lake, Kafka, PostgreSQL, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8cac76c6b23f2063</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Analyst, Applied AI Solutions</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Visa</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>10</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>RAG, Gemini, Copilot, Git, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1f9dd8c06623b61b</t>
+          <t>https://www.indeed.com/viewjob?jk=60aea162a93e864d</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-29.xlsx
+++ b/daily_matches/job_matches_2026-07-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Infrastructure Engineer</t>
+          <t>US LBM AI Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>University of Texas at Austin</t>
+          <t>US LBM Holdings</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.7</v>
+        <v>24.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, Gemini, Copilot, Pinecone, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Prompt Engineering, TensorFlow, PyTorch, OpenCV, YOLO, FastAPI</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8523f45b800a98d2</t>
+          <t>https://www.indeed.com/viewjob?jk=5b0e288f3f830762</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Junior AI Engineer</t>
+          <t>AI Architect/Developer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Trellance</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>24.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Pinecone, Cortex, CI/CD, Snowflake, Databricks, Tableau, Power BI</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, Gemini, Pinecone, TensorFlow, PyTorch, MLflow, FastAPI</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cfec0ee79a36d0b</t>
+          <t>https://www.indeed.com/viewjob?jk=a3c1a9c0b4485739</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SS&amp;C</t>
+          <t>ZoomInfo</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>20</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, S3, Redshift, Docker, Kubernetes, Terraform, Redshift, PostgreSQL, MongoDB, Python</t>
+          <t>Glue, BigQuery, Data Lake, Kinesis, Dataflow, Kubernetes, Apache Airflow, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b734deb5b5c4fd4</t>
+          <t>https://www.indeed.com/viewjob?jk=66a7bb78179837fe</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Global Banking &amp; Markets, AI/ML Technology</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Malvern, AR, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>18.9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Copilot, Docker, Kubernetes, CI/CD, Git, Kafka, NoSQL, SQL</t>
+          <t>S3, Glue, Athena, Data Lake, Kinesis, CI/CD, GitHub Actions, Terraform, Git, Snowflake</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1483d6cac3aa3128</t>
+          <t>https://www.indeed.com/viewjob?jk=ab6ed1b6bcf72320</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Engineering-L2-Dallas-Analyst-Software Engineering</t>
+          <t>Senior Applied ML Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Upstart</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.6</v>
+        <v>17.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, AKS, CI/CD, Snowflake, Databricks, Kafka, Hadoop, Python, SQL</t>
+          <t>Machine Learning Engineer, Generative AI, LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, FastAPI, Docker</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=334f6eafa2204917</t>
+          <t>https://www.indeed.com/viewjob?jk=8fc2ffe711ae71e3</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI/ML Engineer (Senior Associate) - Remote</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Huron Consulting Group</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Malvern, AR, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>17.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, AWS SageMaker, FastAPI, Docker, CI/CD</t>
+          <t>S3, Glue, Athena, Kinesis, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Databricks</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bb67d4138266183</t>
+          <t>https://www.indeed.com/viewjob?jk=7de6f50bed06cb2e</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Backend Engineer _ AI Gateway</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>The Weather Company</t>
+          <t>Woongjin, Inc</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Andover, MA, US USA</t>
+          <t>Englewood Cliffs, NJ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, EC2, Docker, Kubernetes, CI/CD, Git, MongoDB, NoSQL</t>
+          <t>RAG, FastAPI, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Kafka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34cf04c12e423597</t>
+          <t>https://www.indeed.com/viewjob?jk=c10ba632ba10eb20</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Backend Engineer_AI Gateway</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ascendion</t>
+          <t>Sbt Global</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>Englewood Cliffs, NJ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, MongoDB, SQL, R, Java</t>
+          <t>RAG, FastAPI, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Kafka</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a8fea0d6fbd1cf6</t>
+          <t>https://www.indeed.com/viewjob?jk=83ee93c45d38de64</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>540</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>FastAPI, Docker, Kubernetes, GitHub Actions, Git, Kafka, PostgreSQL, MongoDB, Python, SQL</t>
+          <t>Data Scientist, RAG, Kinesis, Docker, Kubernetes, CI/CD, Databricks, PySpark, Kafka, Python</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e5d9c9078da0cac</t>
+          <t>https://www.indeed.com/viewjob?jk=c0833d4fa34d1d99</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Malvern, AR, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>LLaMA, Gemini, Copilot, Prompt Engineering, Git, MySQL, Python, SQL, R, Java</t>
+          <t>AI Engineer, Generative AI, RAG, Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Databricks</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=caf82fff4ed5ef31</t>
+          <t>https://www.indeed.com/viewjob?jk=87c63b7ad7e85d97</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Sr. Salesforce Platform Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>True Classic</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Calabasas, CA, US USA</t>
+          <t>Manhattan Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Prompt Engineering, CI/CD, Git, PostgreSQL, Python, SQL, R, Scala</t>
+          <t>RAG, S3, Docker, CI/CD, Jenkins, GitHub Actions, Git, NoSQL, SQL, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fc9c743e0a349ef</t>
+          <t>https://www.indeed.com/viewjob?jk=863fe2721df72a7a</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Leidos</t>
+          <t>CSC</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Apache Airflow, CI/CD, Git, Databricks, PySpark, Python, SQL, R</t>
+          <t>RAG, Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, SQL, R, Java</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=002cb1d712286720</t>
+          <t>https://www.indeed.com/viewjob?jk=c29e803c14e1c6f3</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Scientist ll - Digital Intelligence</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Socure</t>
+          <t>540</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, XGBoost, Git, Databricks, PySpark, Python, SQL</t>
+          <t>Kinesis, MLflow, CI/CD, Terraform, Databricks, PySpark, Kafka, Python, SQL, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ba5b1d946790692</t>
+          <t>https://www.indeed.com/viewjob?jk=9b7615dc336b2258</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior AI Engineer, Conversational AI &amp; Agentic Systems - Voice Required</t>
+          <t>Senior Software Engineer ( Seattle/Provo Hybrid)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Blooming Health</t>
+          <t>Press Ganey</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Provo, UT, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Prompt Engineering, Docker, Kubernetes, Kafka, PostgreSQL, Python, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e7979301289c696</t>
+          <t>https://www.indeed.com/viewjob?jk=03d04a01c7bf9fa1</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. PKI, HashiCorp Operations Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, S3, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+          <t>Generative AI, RAG, Gemini, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=262c117f16e0e490</t>
+          <t>https://www.indeed.com/viewjob?jk=113faecc285e46f7</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Data Scientist II</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Delinea</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>North Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Terraform, Kafka, NoSQL, SQL, R, Scala, Optimization</t>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, Tableau, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=749e23d0b9c802de</t>
+          <t>https://www.indeed.com/viewjob?jk=dcbabbf72dc606a5</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Full Stack AI Software Engineer</t>
+          <t>Cloud Engineer IV</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Freedom Mortgage</t>
+          <t>Applied Information Sciences</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Marlton, NJ, US USA</t>
+          <t>College Park, MD, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, Kubernetes, Git, Python, SQL, R, Java, Scala</t>
+          <t>Docker, Kubernetes, AKS, CI/CD, Jenkins, Terraform, Git, Power BI, R, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bf2e8dc44b5e2c3</t>
+          <t>https://www.indeed.com/viewjob?jk=b166ea3ed0251cff</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Big Data and Cloud</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Vistar Media</t>
+          <t>MIAX</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, Git, BigQuery, Kafka, Python, SQL, R, Scala</t>
+          <t>RAG, Snowflake, Kafka, Hadoop, PostgreSQL, MySQL, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=488613eddf36a539</t>
+          <t>https://www.indeed.com/viewjob?jk=c9bbe4fa9a69f979</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Cetera Financial Group</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, FastAPI, Docker, CI/CD, Git, PostgreSQL, Python, SQL, R</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Copilot, Hugging Face, CI/CD, Git, Python, R</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d51bf7d637343fc1</t>
+          <t>https://www.indeed.com/viewjob?jk=1b26f74ddfad8a5c</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data &amp; Analytics Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Peterson Caterpillar</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>San Leandro, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, Snowflake, PySpark, Power BI, Python, SQL, R, Scala, Optimization</t>
+          <t>AI Engineer, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6d496ec22a09d07</t>
+          <t>https://www.indeed.com/viewjob?jk=0d688175b6e26701</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reliability Engineer</t>
+          <t>AI Software Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>AVEVA</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Lake Forest, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, CI/CD, Terraform, Python, SQL, R, Java</t>
+          <t>RAG, Copilot, Prompt Engineering, TensorFlow, PyTorch, AKS, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eed01edaf71cb8e2</t>
+          <t>https://www.indeed.com/viewjob?jk=2e208157fe3946f0</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Reliability Engineer</t>
+          <t>Software Test Analyst Sr II</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>IDEXX Laboratories</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, CI/CD, Terraform, Python, SQL, R, Java</t>
+          <t>Data Scientist, RAG, Data Lake, GitHub Actions, Git, Snowflake, Databricks, Python, SQL, R</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=894e91b00b84ec52</t>
+          <t>https://www.indeed.com/viewjob?jk=b0376f59bf79251e</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Reliability Engineer</t>
+          <t>Applied AI Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Ovivo</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, CI/CD, Terraform, Python, SQL, R, Java</t>
+          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, Git, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=015ed88153be94e8</t>
+          <t>https://www.indeed.com/viewjob?jk=b232e9db1d947c12</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Reliability Engineer</t>
+          <t>Software Engineer Intern (1st Shift) - Fall 2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>First Solar</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Perrysburg, OH, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, CI/CD, Terraform, Python, SQL, R, Java</t>
+          <t>Generative AI, RAG, Kubernetes, Apache Airflow, CI/CD, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9330891927556077</t>
+          <t>https://www.indeed.com/viewjob?jk=c9533f4bcb9dbf61</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sr Data Analyst</t>
+          <t>Software Engineer III- Python, Databricks</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Guild Mortgage Company LLC</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RAG, Snowflake, MySQL, MongoDB, Cassandra, NoSQL, SQL, R, Scala</t>
+          <t>RAG, Databricks, Kafka, MongoDB, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,7 +1336,77 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60aea162a93e864d</t>
+          <t>https://www.indeed.com/viewjob?jk=60932333f665bc9b</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Data Engineer III - Python / AWS / SQL</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>10</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Git, NoSQL, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9f82eb533e1ade58</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Associate Data Scientist I</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>TTX</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>10</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Git, Tableau, Power BI, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bafb4af4bdf3d254</t>
         </is>
       </c>
     </row>
